--- a/src/data/Articulos certificados.xlsx
+++ b/src/data/Articulos certificados.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2162"/>
+  <dimension ref="A1:C2165"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24181,9 +24181,42 @@
         <v>EFR diaphragm dosing pump 3ph 1044 - 1254 l/h (276 - 331gph) 5bar (73psi) Inox 1 1/4 Atex motor</v>
       </c>
     </row>
+    <row r="2163">
+      <c r="A2163" t="str">
+        <v>60-AD41-D69PIK-000-000</v>
+      </c>
+      <c r="B2163" t="str">
+        <v>Dostec-40d membrana 3ph 44-32 l/h 15bar PP-FPM-INOX-3/4"</v>
+      </c>
+      <c r="C2163" t="str">
+        <v>Dostec-40d diaphragm 3ph 44-32 l/h 15bar PP-FPM-SS-3/4"</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="str">
+        <v>60-AD31-D69PEL-000-000</v>
+      </c>
+      <c r="B2164" t="str">
+        <v>Dostec-40d bomba dosificadora membrana 3ph 22-15,2l/h 16b;</v>
+      </c>
+      <c r="C2164" t="str">
+        <v>Dostec-40d diaphragm dosing pump 3ph 22-15,2 l/h 16bar PP-EI</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="str">
+        <v>73-AC2D42-D69PBM-000-000</v>
+      </c>
+      <c r="B2165" t="str">
+        <v>Dostec AC membrana 92-68 l/h 10bar PP-FPM-BORO-3/4"</v>
+      </c>
+      <c r="C2165" t="str">
+        <v>Dostec AC diaphragm 92-68 l/h 10bar PP-FPM-BORO-3/4"</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2165"/>
   </ignoredErrors>
 </worksheet>
 </file>